--- a/07-aws-cloud-compliance/07-aws-cloud-compliance.xlsx
+++ b/07-aws-cloud-compliance/07-aws-cloud-compliance.xlsx
@@ -77,7 +77,7 @@
     <t xml:space="preserve">Approved by</t>
   </si>
   <si>
-    <t xml:space="preserve">Jerry Olugboye, Chief Executive Officer</t>
+    <t xml:space="preserve">Jerry Gold, Chief Executive Officer</t>
   </si>
   <si>
     <t xml:space="preserve">Inputs consumed</t>
